--- a/outputs/Block2_National_Nested_OOF_v12.xlsx
+++ b/outputs/Block2_National_Nested_OOF_v12.xlsx
@@ -2187,7 +2187,7 @@
         <v>50</v>
       </c>
       <c r="I44">
-        <v>0.4773119999999993</v>
+        <v>0.4773119999999992</v>
       </c>
       <c r="J44">
         <v>0.4815039999999993</v>
@@ -3482,7 +3482,7 @@
         <v>0.4795759999999995</v>
       </c>
       <c r="J78">
-        <v>0.4830239999999993</v>
+        <v>0.4830239999999994</v>
       </c>
       <c r="K78">
         <v>0.4667102705793568</v>
@@ -5420,7 +5420,7 @@
         <v>0.4821079999999993</v>
       </c>
       <c r="J129">
-        <v>0.4865799999999995</v>
+        <v>0.4865799999999994</v>
       </c>
       <c r="K129">
         <v>0.4693095837053707</v>

--- a/outputs/Block2_National_Nested_OOF_v12.xlsx
+++ b/outputs/Block2_National_Nested_OOF_v12.xlsx
@@ -717,7 +717,7 @@
         <v>0.4903679999999988</v>
       </c>
       <c r="J8">
-        <v>0.4821359999999988</v>
+        <v>0.4821359999999989</v>
       </c>
       <c r="K8">
         <v>0.4828693426768441</v>
@@ -790,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="I10">
-        <v>0.464931999999999</v>
+        <v>0.4649319999999991</v>
       </c>
       <c r="J10">
         <v>0.4749799999999992</v>

--- a/outputs/Block2_National_Nested_OOF_v12.xlsx
+++ b/outputs/Block2_National_Nested_OOF_v12.xlsx
@@ -641,7 +641,7 @@
         <v>0.4867479999999996</v>
       </c>
       <c r="J6">
-        <v>0.4846759999999996</v>
+        <v>0.4846759999999995</v>
       </c>
       <c r="K6">
         <v>0.482279686201995</v>
@@ -717,7 +717,7 @@
         <v>0.4903679999999988</v>
       </c>
       <c r="J8">
-        <v>0.4821359999999989</v>
+        <v>0.4821359999999988</v>
       </c>
       <c r="K8">
         <v>0.4828693426768441</v>

--- a/outputs/Block2_National_Nested_OOF_v12.xlsx
+++ b/outputs/Block2_National_Nested_OOF_v12.xlsx
@@ -641,7 +641,7 @@
         <v>0.4867479999999996</v>
       </c>
       <c r="J6">
-        <v>0.4846759999999995</v>
+        <v>0.4846759999999996</v>
       </c>
       <c r="K6">
         <v>0.482279686201995</v>
@@ -790,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="I10">
-        <v>0.4649319999999991</v>
+        <v>0.464931999999999</v>
       </c>
       <c r="J10">
         <v>0.4749799999999992</v>
